--- a/Pune-September-2025.xlsx
+++ b/Pune-September-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="108">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Pune</t>
   </si>
   <si>
@@ -262,22 +265,19 @@
     <t>MH02GH7486</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Invicto</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>INVICTO</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>EC3</t>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>DZIRE</t>
-  </si>
-  <si>
-    <t>DZIRE PETROL</t>
   </si>
   <si>
     <t>URBANIA</t>
@@ -699,10 +699,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z55"/>
+  <dimension ref="A1:AA55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -781,25 +781,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2">
         <v>44899</v>
@@ -862,24 +865,24 @@
         <v>35.07</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="2">
         <v>44899</v>
@@ -942,24 +945,24 @@
         <v>47.09</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>203</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2">
         <v>44686</v>
@@ -1022,24 +1025,24 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>204</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
         <v>90</v>
@@ -1102,24 +1105,24 @@
         <v>51.19</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s">
         <v>90</v>
@@ -1182,24 +1185,24 @@
         <v>53.91</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="2">
         <v>44963</v>
@@ -1262,24 +1265,24 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>207</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s">
         <v>91</v>
@@ -1342,24 +1345,24 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>208</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -1422,24 +1425,24 @@
         <v>62.4</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>209</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
         <v>93</v>
@@ -1502,24 +1505,24 @@
         <v>55.87</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>210</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2">
         <v>43471</v>
@@ -1582,24 +1585,24 @@
         <v>39.27</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>211</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" t="s">
         <v>94</v>
@@ -1662,24 +1665,24 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>212</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s">
         <v>95</v>
@@ -1742,24 +1745,24 @@
         <v>29.32</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>213</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s">
         <v>95</v>
@@ -1822,24 +1825,24 @@
         <v>32.79</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G15" t="s">
         <v>96</v>
@@ -1902,24 +1905,24 @@
         <v>33.98</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>215</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
         <v>97</v>
@@ -1987,19 +1990,19 @@
         <v>216</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
         <v>97</v>
@@ -2067,19 +2070,19 @@
         <v>217</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2">
         <v>45451</v>
@@ -2147,19 +2150,19 @@
         <v>218</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2">
         <v>45451</v>
@@ -2227,19 +2230,19 @@
         <v>219</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G20" t="s">
         <v>98</v>
@@ -2307,19 +2310,19 @@
         <v>220</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G21" s="2">
         <v>45359</v>
@@ -2387,19 +2390,19 @@
         <v>221</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G22" t="s">
         <v>99</v>
@@ -2467,19 +2470,19 @@
         <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G23" s="2">
         <v>44840</v>
@@ -2547,19 +2550,19 @@
         <v>223</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G24" s="2">
         <v>44840</v>
@@ -2627,19 +2630,19 @@
         <v>224</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" s="2">
         <v>44840</v>
@@ -2707,19 +2710,19 @@
         <v>225</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26" s="2">
         <v>44840</v>
@@ -2787,19 +2790,19 @@
         <v>226</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G27" s="2">
         <v>44840</v>
@@ -2867,19 +2870,19 @@
         <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
         <v>100</v>
@@ -2947,19 +2950,19 @@
         <v>228</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
         <v>100</v>
@@ -3027,19 +3030,19 @@
         <v>229</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G30" t="s">
         <v>100</v>
@@ -3107,19 +3110,19 @@
         <v>230</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G31" s="2">
         <v>44749</v>
@@ -3187,19 +3190,19 @@
         <v>231</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G32" s="2">
         <v>44749</v>
@@ -3267,19 +3270,19 @@
         <v>232</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G33" s="2">
         <v>44749</v>
@@ -3347,19 +3350,19 @@
         <v>233</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G34" s="2">
         <v>44749</v>
@@ -3427,19 +3430,19 @@
         <v>234</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G35" s="2">
         <v>44749</v>
@@ -3507,19 +3510,19 @@
         <v>235</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G36" s="2">
         <v>44749</v>
@@ -3587,19 +3590,19 @@
         <v>236</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G37" s="2">
         <v>44749</v>
@@ -3667,19 +3670,19 @@
         <v>237</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G38" s="2">
         <v>44749</v>
@@ -3747,19 +3750,19 @@
         <v>238</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G39" s="2">
         <v>44749</v>
@@ -3827,19 +3830,19 @@
         <v>239</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2025</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G40" s="2">
         <v>44749</v>
@@ -3907,19 +3910,19 @@
         <v>240</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G41" t="s">
         <v>101</v>
@@ -3987,19 +3990,19 @@
         <v>241</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G42" t="s">
         <v>101</v>
@@ -4067,19 +4070,19 @@
         <v>242</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s">
         <v>102</v>
@@ -4147,19 +4150,19 @@
         <v>243</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G44" s="2">
         <v>45080</v>
@@ -4227,19 +4230,19 @@
         <v>244</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G45" t="s">
         <v>102</v>
@@ -4307,16 +4310,16 @@
         <v>245</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
         <v>87</v>
@@ -4387,16 +4390,16 @@
         <v>246</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
         <v>87</v>
@@ -4467,16 +4470,16 @@
         <v>247</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>2025</v>
       </c>
       <c r="E48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
         <v>87</v>
@@ -4547,16 +4550,16 @@
         <v>248</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s">
         <v>87</v>
@@ -4627,16 +4630,16 @@
         <v>249</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50">
         <v>2025</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F50" t="s">
         <v>87</v>
@@ -4707,16 +4710,16 @@
         <v>250</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
         <v>87</v>
@@ -4787,16 +4790,16 @@
         <v>251</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52">
         <v>2025</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
         <v>88</v>
@@ -4867,16 +4870,16 @@
         <v>252</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53">
         <v>2025</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
         <v>89</v>
@@ -4947,16 +4950,16 @@
         <v>253</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>2025</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
         <v>89</v>
@@ -5027,16 +5030,16 @@
         <v>254</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55">
         <v>2025</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
         <v>89</v>
